--- a/assets/templates/employee_import_template.xlsx
+++ b/assets/templates/employee_import_template.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Employees" sheetId="1" r:id="Rea3e4b1f08cb40a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WorkExperience" sheetId="2" r:id="Rdef71fbd66304fd4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Education" sheetId="3" r:id="R960abcac6e184fa6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Employees" sheetId="1" r:id="R482b0a80621241e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WorkExperience" sheetId="2" r:id="R857dbf76ab1b4ce4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Education" sheetId="3" r:id="Rfed3262eef784fa8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -373,8 +373,8 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
   </x:cols>
@@ -401,16 +401,16 @@
         <x:v>E0001</x:v>
       </x:c>
       <x:c r="B2" s="24" t="str">
-        <x:v>张三</x:v>
+        <x:v>周予安（虚构）</x:v>
       </x:c>
       <x:c r="C2" s="24" t="str">
-        <x:v>zhangsan@example.com</x:v>
+        <x:v>test.employee1@example.com</x:v>
       </x:c>
       <x:c r="D2" s="24" t="str">
-        <x:v>商业化</x:v>
+        <x:v>免疫研究部</x:v>
       </x:c>
       <x:c r="E2" s="25" t="str">
-        <x:v>区域经理</x:v>
+        <x:v>免疫学研究员</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -423,7 +423,7 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="40" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
@@ -451,10 +451,10 @@
         <x:v>E0001</x:v>
       </x:c>
       <x:c r="B2" s="24" t="str">
-        <x:v>示例公司</x:v>
+        <x:v>明澈免疫生物医药有限公司</x:v>
       </x:c>
       <x:c r="C2" s="24" t="str">
-        <x:v>销售主管</x:v>
+        <x:v>免疫学研究员</x:v>
       </x:c>
       <x:c r="D2" s="26" t="n">
         <x:v>43831</x:v>
@@ -4491,10 +4491,10 @@
         <x:v>E0001</x:v>
       </x:c>
       <x:c r="B2" s="24" t="str">
-        <x:v>示例大学</x:v>
+        <x:v>北京大学</x:v>
       </x:c>
       <x:c r="C2" s="24" t="str">
-        <x:v>市场营销</x:v>
+        <x:v>免疫学</x:v>
       </x:c>
       <x:c r="D2" s="26" t="n">
         <x:v>42614</x:v>
